--- a/docs/video-ingestion/WeaveSense_完整开发任务清单_执行版.xlsx
+++ b/docs/video-ingestion/WeaveSense_完整开发任务清单_执行版.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付总览" sheetId="1" r:id="R136bc8a8c7804209"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发任务" sheetId="2" r:id="R1f4c4d04ecaf40a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="3" r:id="R10520d9a51dc4c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求与验收" sheetId="4" r:id="Rdcb08cb9258f4391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="端到端用例" sheetId="5" r:id="R622a6dfa3ec14585"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基线与约定" sheetId="6" r:id="R2d166d00c2d24597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付总览" sheetId="1" r:id="R8cf8093762d4408d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发任务" sheetId="2" r:id="Rab3acdf2aa52495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="3" r:id="R34186f59833a4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求与验收" sheetId="4" r:id="Rd2c9b820de704a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="端到端用例" sheetId="5" r:id="R37d91068ce0a402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基线与约定" sheetId="6" r:id="R31a47696b34a471a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1564,14 +1564,14 @@
       </x:c>
       <x:c r="D39" s="2" t="n">
         <x:f>COUNTIFS('端到端用例'!$C$7:$C$36,"P0",'端到端用例'!$H$7:$H$36,"通过")+COUNTIFS('端到端用例'!$C$7:$C$36,"P1",'端到端用例'!$H$7:$H$36,"通过")</x:f>
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E39" s="2" t="str">
         <x:v>尚未通过</x:v>
       </x:c>
       <x:c r="F39" s="2" t="n">
         <x:f>B39-D39</x:f>
-        <x:v>29</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G39" s="2"/>
       <x:c r="H39" s="2"/>
@@ -1913,7 +1913,7 @@
 逐条验收：通过 2。</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="69" hidden="0" customHeight="1">
+    <x:row r="8" ht="107" hidden="0" customHeight="1">
       <x:c r="A8" s="18" t="str">
         <x:v>COL-002</x:v>
       </x:c>
@@ -1960,12 +1960,13 @@
       <x:c r="P8" s="19" t="str"/>
       <x:c r="Q8" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：FND-002
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：FND-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-002。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="69" hidden="0" customHeight="1">
+    <x:row r="9" ht="107" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
         <x:v>FND-001</x:v>
       </x:c>
@@ -2010,12 +2011,13 @@
       <x:c r="P9" s="19" t="str"/>
       <x:c r="Q9" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-相关外部验收边界：X-DOMAIN；逐条适用说明见独立矩阵。
+原业务定义待确认；通用开发配置及测试不代替实际行业、样本或负责人。
+原条款待输入：选定实际行业、5–10个问题、来源使用/保留规则和复核/发布负责人。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 FND-001。
 逐条验收：阻塞 1。</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="82" hidden="0" customHeight="1">
+    <x:row r="10" ht="95" hidden="0" customHeight="1">
       <x:c r="A10" s="18" t="str">
         <x:v>FND-002</x:v>
       </x:c>
@@ -2062,12 +2064,13 @@
       <x:c r="P10" s="19" t="str"/>
       <x:c r="Q10" s="19" t="str">
         <x:v>【执行记录】
-自身技术边界/契约文档已核对，但 K-001 依赖未冻结行业的 FND-001；FND-002 经 K-001 传递阻塞。不得绕过原依赖图标已完成。
-前置任务未正式闭合：K-001
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 FND-002。
 逐条验收：执行中 1。</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="95" hidden="0" customHeight="1">
+    <x:row r="11" ht="132" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>FND-003</x:v>
       </x:c>
@@ -2114,13 +2117,14 @@
       <x:c r="P11" s="19" t="str"/>
       <x:c r="Q11" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：FND-001, K-001
-相关外部验收边界：X-DOMAIN, X-SAMPLES；逐条适用说明见独立矩阵。
+原业务定义待确认；通用开发配置及测试不代替实际行业、样本或负责人。
+原条款待输入：冻结覆盖原风险类别的授权双平台样本、人工标签/答案/评分及负向问题；默认建议规模可由M0校准。
+原直接依赖未签收：FND-001, K-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 FND-003。
 逐条验收：阻塞 1。</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="82" hidden="0" customHeight="1">
+    <x:row r="12" ht="95" hidden="0" customHeight="1">
       <x:c r="A12" s="18" t="str">
         <x:v>FND-004</x:v>
       </x:c>
@@ -2143,7 +2147,7 @@
         <x:v>integration</x:v>
       </x:c>
       <x:c r="H12" s="19" t="str">
-        <x:v>阻塞</x:v>
+        <x:v>待验收</x:v>
       </x:c>
       <x:c r="I12" s="24" t="n">
         <x:v>1</x:v>
@@ -2157,7 +2161,7 @@
       </x:c>
       <x:c r="L12" s="18" t="str">
         <x:f>IF(H12="已完成","已完成",IF(D12="P2","后续规划",IF(H12="阻塞","处理阻塞",IF(H12="暂停","已暂停",IF(K12&gt;0,"等待依赖",IF(G12="","待指派",IF(H12="待验收","待验收","可推进")))))))</x:f>
-        <x:v>处理阻塞</x:v>
+        <x:v>等待依赖</x:v>
       </x:c>
       <x:c r="M12" s="18" t="str">
         <x:v>R26</x:v>
@@ -2167,13 +2171,13 @@
       <x:c r="P12" s="19" t="str"/>
       <x:c r="Q12" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：K-001
-相关外部验收边界：X-DEPLOY；逐条适用说明见独立矩阵。
-逐条验收：阻塞 1。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="95" hidden="0" customHeight="1">
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 FND-004。
+逐条验收：通过 1。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="132" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
         <x:v>FND-005</x:v>
       </x:c>
@@ -2220,9 +2224,10 @@
       <x:c r="P13" s="19" t="str"/>
       <x:c r="Q13" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：FND-001, K-001
-相关外部验收边界：X-DOMAIN, X-SAMPLES, X-PLATFORM, X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：实际双平台少量发现/下载/处理能力与目标环境耗时资源测量；受控adapter/宿主执行证据不冒充平台实测。
+原直接依赖未签收：FND-001, K-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 FND-005。
 逐条验收：阻塞 1。</x:v>
       </x:c>
     </x:row>
@@ -2274,7 +2279,7 @@
 逐条验收：通过 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="82" hidden="0" customHeight="1">
+    <x:row r="15" ht="95" hidden="0" customHeight="1">
       <x:c r="A15" s="16" t="str">
         <x:v>K-001</x:v>
       </x:c>
@@ -2321,12 +2326,13 @@
       <x:c r="P15" s="19" t="str"/>
       <x:c r="Q15" s="19" t="str">
         <x:v>【执行记录】
-自身技术边界/契约文档已核对，但 K-001 依赖未冻结行业的 FND-001；FND-002 经 K-001 传递阻塞。不得绕过原依赖图标已完成。
-前置任务未正式闭合：FND-001
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：FND-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-001。
 逐条验收：执行中 2。</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="69" hidden="0" customHeight="1">
+    <x:row r="16" ht="107" hidden="0" customHeight="1">
       <x:c r="A16" s="18" t="str">
         <x:v>CFG-001</x:v>
       </x:c>
@@ -2373,12 +2379,13 @@
       <x:c r="P16" s="19" t="str"/>
       <x:c r="Q16" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：FND-001, FND-002, COL-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：FND-001, FND-002, COL-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 CFG-001。
 逐条验收：执行中 1。</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="69" hidden="0" customHeight="1">
+    <x:row r="17" ht="107" hidden="0" customHeight="1">
       <x:c r="A17" s="16" t="str">
         <x:v>COL-003</x:v>
       </x:c>
@@ -2425,12 +2432,13 @@
       <x:c r="P17" s="19" t="str"/>
       <x:c r="Q17" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-002, K-002
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-002, K-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-003。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="69" hidden="0" customHeight="1">
+    <x:row r="18" ht="107" hidden="0" customHeight="1">
       <x:c r="A18" s="18" t="str">
         <x:v>COL-004</x:v>
       </x:c>
@@ -2477,12 +2485,13 @@
       <x:c r="P18" s="19" t="str"/>
       <x:c r="Q18" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-003, CFG-001
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-003, CFG-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-004。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="69" hidden="0" customHeight="1">
+    <x:row r="19" ht="107" hidden="0" customHeight="1">
       <x:c r="A19" s="16" t="str">
         <x:v>COL-005</x:v>
       </x:c>
@@ -2529,12 +2538,13 @@
       <x:c r="P19" s="19" t="str"/>
       <x:c r="Q19" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-002, COL-004
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-002, COL-004。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-005。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="82" hidden="0" customHeight="1">
+    <x:row r="20" ht="107" hidden="0" customHeight="1">
       <x:c r="A20" s="18" t="str">
         <x:v>COL-006</x:v>
       </x:c>
@@ -2581,13 +2591,13 @@
       <x:c r="P20" s="19" t="str"/>
       <x:c r="Q20" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-002, COL-005, FND-005
-相关外部验收边界：X-PLATFORM；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-002, COL-005, FND-005。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-006。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="82" hidden="0" customHeight="1">
+    <x:row r="21" ht="107" hidden="0" customHeight="1">
       <x:c r="A21" s="16" t="str">
         <x:v>COL-007</x:v>
       </x:c>
@@ -2634,13 +2644,13 @@
       <x:c r="P21" s="19" t="str"/>
       <x:c r="Q21" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-006
-相关外部验收边界：X-PLATFORM；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-006。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-007。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="82" hidden="0" customHeight="1">
+    <x:row r="22" ht="107" hidden="0" customHeight="1">
       <x:c r="A22" s="18" t="str">
         <x:v>COL-008</x:v>
       </x:c>
@@ -2687,13 +2697,13 @@
       <x:c r="P22" s="19" t="str"/>
       <x:c r="Q22" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-004, COL-007
-相关外部验收边界：X-PLATFORM；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-004, COL-007。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-008。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="82" hidden="0" customHeight="1">
+    <x:row r="23" ht="107" hidden="0" customHeight="1">
       <x:c r="A23" s="16" t="str">
         <x:v>COL-009</x:v>
       </x:c>
@@ -2740,13 +2750,13 @@
       <x:c r="P23" s="19" t="str"/>
       <x:c r="Q23" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-004, COL-007
-相关外部验收边界：X-PLATFORM；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-004, COL-007。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-009。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="69" hidden="0" customHeight="1">
+    <x:row r="24" ht="107" hidden="0" customHeight="1">
       <x:c r="A24" s="18" t="str">
         <x:v>COL-010</x:v>
       </x:c>
@@ -2793,12 +2803,13 @@
       <x:c r="P24" s="19" t="str"/>
       <x:c r="Q24" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-003, COL-009
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-003, COL-009。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-010。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="82" hidden="0" customHeight="1">
+    <x:row r="25" ht="107" hidden="0" customHeight="1">
       <x:c r="A25" s="16" t="str">
         <x:v>COL-011</x:v>
       </x:c>
@@ -2845,13 +2856,13 @@
       <x:c r="P25" s="19" t="str"/>
       <x:c r="Q25" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-004, COL-010
-相关外部验收边界：X-PLATFORM；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-004, COL-010。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-011。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="69" hidden="0" customHeight="1">
+    <x:row r="26" ht="107" hidden="0" customHeight="1">
       <x:c r="A26" s="18" t="str">
         <x:v>COL-012</x:v>
       </x:c>
@@ -2898,12 +2909,13 @@
       <x:c r="P26" s="19" t="str"/>
       <x:c r="Q26" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-003, COL-008, COL-010
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-003, COL-008, COL-010。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-012。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="69" hidden="0" customHeight="1">
+    <x:row r="27" ht="107" hidden="0" customHeight="1">
       <x:c r="A27" s="16" t="str">
         <x:v>COL-013</x:v>
       </x:c>
@@ -2950,12 +2962,13 @@
       <x:c r="P27" s="19" t="str"/>
       <x:c r="Q27" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-006, COL-012
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-006, COL-012。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-013。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="69" hidden="0" customHeight="1">
+    <x:row r="28" ht="107" hidden="0" customHeight="1">
       <x:c r="A28" s="18" t="str">
         <x:v>COL-014</x:v>
       </x:c>
@@ -3002,12 +3015,13 @@
       <x:c r="P28" s="19" t="str"/>
       <x:c r="Q28" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-012, COL-013
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-012, COL-013。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-014。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="69" hidden="0" customHeight="1">
+    <x:row r="29" ht="107" hidden="0" customHeight="1">
       <x:c r="A29" s="16" t="str">
         <x:v>COL-015</x:v>
       </x:c>
@@ -3054,12 +3068,13 @@
       <x:c r="P29" s="19" t="str"/>
       <x:c r="Q29" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-006, COL-012, COL-014, COL-016
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-006, COL-012, COL-014, COL-016。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-015。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="69" hidden="0" customHeight="1">
+    <x:row r="30" ht="107" hidden="0" customHeight="1">
       <x:c r="A30" s="18" t="str">
         <x:v>COL-016</x:v>
       </x:c>
@@ -3106,12 +3121,13 @@
       <x:c r="P30" s="19" t="str"/>
       <x:c r="Q30" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-002, COL-003, K-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-002, COL-003, K-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-016。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="69" hidden="0" customHeight="1">
+    <x:row r="31" ht="107" hidden="0" customHeight="1">
       <x:c r="A31" s="16" t="str">
         <x:v>COL-017</x:v>
       </x:c>
@@ -3158,12 +3174,13 @@
       <x:c r="P31" s="19" t="str"/>
       <x:c r="Q31" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-012, COL-014
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-012, COL-014。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-017。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="69" hidden="0" customHeight="1">
+    <x:row r="32" ht="107" hidden="0" customHeight="1">
       <x:c r="A32" s="18" t="str">
         <x:v>COL-018</x:v>
       </x:c>
@@ -3210,12 +3227,13 @@
       <x:c r="P32" s="19" t="str"/>
       <x:c r="Q32" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-006, COL-014, COL-017
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-006, COL-014, COL-017。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-018。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="69" hidden="0" customHeight="1">
+    <x:row r="33" ht="107" hidden="0" customHeight="1">
       <x:c r="A33" s="16" t="str">
         <x:v>COL-019</x:v>
       </x:c>
@@ -3262,12 +3280,13 @@
       <x:c r="P33" s="19" t="str"/>
       <x:c r="Q33" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-013, COL-014, COL-017, COL-018
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-013, COL-014, COL-017, COL-018。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-019。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="69" hidden="0" customHeight="1">
+    <x:row r="34" ht="107" hidden="0" customHeight="1">
       <x:c r="A34" s="18" t="str">
         <x:v>COL-020</x:v>
       </x:c>
@@ -3314,12 +3333,13 @@
       <x:c r="P34" s="19" t="str"/>
       <x:c r="Q34" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-011, COL-012
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-011, COL-012。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-020。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="69" hidden="0" customHeight="1">
+    <x:row r="35" ht="95" hidden="0" customHeight="1">
       <x:c r="A35" s="16" t="str">
         <x:v>K-002</x:v>
       </x:c>
@@ -3366,12 +3386,13 @@
       <x:c r="P35" s="19" t="str"/>
       <x:c r="Q35" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-001, FND-002
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-001, FND-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-002。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="69" hidden="0" customHeight="1">
+    <x:row r="36" ht="95" hidden="0" customHeight="1">
       <x:c r="A36" s="18" t="str">
         <x:v>K-003</x:v>
       </x:c>
@@ -3418,12 +3439,13 @@
       <x:c r="P36" s="19" t="str"/>
       <x:c r="Q36" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-001, K-002, COL-002
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-001, K-002, COL-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-003。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="82" hidden="0" customHeight="1">
+    <x:row r="37" ht="120" hidden="0" customHeight="1">
       <x:c r="A37" s="16" t="str">
         <x:v>K-027</x:v>
       </x:c>
@@ -3470,13 +3492,14 @@
       <x:c r="P37" s="19" t="str"/>
       <x:c r="Q37" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：FND-001, K-001, CFG-001
-相关外部验收边界：X-DOMAIN；逐条适用说明见独立矩阵。
+原业务定义待确认；通用开发配置及测试不代替实际行业、样本或负责人。
+原条款待输入：确认实际首发行业并复核对应profile/词表/边界样例；通用开发profile不是实际行业冻结。
+原直接依赖未签收：FND-001, K-001, CFG-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-027。
 逐条验收：阻塞 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="69" hidden="0" customHeight="1">
+    <x:row r="38" ht="95" hidden="0" customHeight="1">
       <x:c r="A38" s="18" t="str">
         <x:v>IF-002</x:v>
       </x:c>
@@ -3523,12 +3546,13 @@
       <x:c r="P38" s="19" t="str"/>
       <x:c r="Q38" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-002, K-002
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-002, K-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-002。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="69" hidden="0" customHeight="1">
+    <x:row r="39" ht="95" hidden="0" customHeight="1">
       <x:c r="A39" s="16" t="str">
         <x:v>IF-003</x:v>
       </x:c>
@@ -3575,12 +3599,13 @@
       <x:c r="P39" s="19" t="str"/>
       <x:c r="Q39" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-002, K-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-002, K-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-003。
 逐条验收：执行中 5。</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="69" hidden="0" customHeight="1">
+    <x:row r="40" ht="95" hidden="0" customHeight="1">
       <x:c r="A40" s="18" t="str">
         <x:v>IF-004</x:v>
       </x:c>
@@ -3627,12 +3652,13 @@
       <x:c r="P40" s="19" t="str"/>
       <x:c r="Q40" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-003, COL-005, COL-012
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-003, COL-005, COL-012。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-004。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="69" hidden="0" customHeight="1">
+    <x:row r="41" ht="82" hidden="0" customHeight="1">
       <x:c r="A41" s="16" t="str">
         <x:v>IF-005</x:v>
       </x:c>
@@ -3679,12 +3705,13 @@
       <x:c r="P41" s="19" t="str"/>
       <x:c r="Q41" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-005。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="82" hidden="0" customHeight="1">
+    <x:row r="42" ht="95" hidden="0" customHeight="1">
       <x:c r="A42" s="18" t="str">
         <x:v>IF-006</x:v>
       </x:c>
@@ -3731,12 +3758,13 @@
       <x:c r="P42" s="19" t="str"/>
       <x:c r="Q42" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-004, IF-005, COL-008, COL-009, COL-012, COL-013
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-004, IF-005, COL-008, COL-009, COL-012, COL-013。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-006。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="69" hidden="0" customHeight="1">
+    <x:row r="43" ht="95" hidden="0" customHeight="1">
       <x:c r="A43" s="16" t="str">
         <x:v>IF-007</x:v>
       </x:c>
@@ -3783,12 +3811,13 @@
       <x:c r="P43" s="19" t="str"/>
       <x:c r="Q43" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-006, COL-013, COL-019
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-006, COL-013, COL-019。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-007。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="69" hidden="0" customHeight="1">
+    <x:row r="44" ht="95" hidden="0" customHeight="1">
       <x:c r="A44" s="18" t="str">
         <x:v>IF-008</x:v>
       </x:c>
@@ -3835,12 +3864,13 @@
       <x:c r="P44" s="19" t="str"/>
       <x:c r="Q44" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-004, IF-005, COL-025
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-004, IF-005, COL-025。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-008。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="69" hidden="0" customHeight="1">
+    <x:row r="45" ht="95" hidden="0" customHeight="1">
       <x:c r="A45" s="16" t="str">
         <x:v>IF-009</x:v>
       </x:c>
@@ -3887,12 +3917,13 @@
       <x:c r="P45" s="19" t="str"/>
       <x:c r="Q45" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-006, K-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-006, K-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-009。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="82" hidden="0" customHeight="1">
+    <x:row r="46" ht="95" hidden="0" customHeight="1">
       <x:c r="A46" s="18" t="str">
         <x:v>IF-010</x:v>
       </x:c>
@@ -3939,8 +3970,9 @@
       <x:c r="P46" s="19" t="str"/>
       <x:c r="Q46" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-003, IF-004, COL-012, COL-017, K-002, K-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-003, IF-004, COL-012, COL-017, K-002, K-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-010。
 逐条验收：执行中 5。</x:v>
       </x:c>
     </x:row>
@@ -3991,13 +4023,13 @@
       <x:c r="P47" s="19" t="str"/>
       <x:c r="Q47" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-003, COL-004, COL-005, COL-008, COL-009, COL-011, K-001
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-003, COL-004, COL-005, COL-008, COL-009, COL-011, K-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-017。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="82" hidden="0" customHeight="1">
+    <x:row r="48" ht="107" hidden="0" customHeight="1">
       <x:c r="A48" s="18" t="str">
         <x:v>COL-025</x:v>
       </x:c>
@@ -4044,13 +4076,13 @@
       <x:c r="P48" s="19" t="str"/>
       <x:c r="Q48" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-006, COL-015, COL-017
-相关外部验收边界：X-DEPLOY；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-006, COL-015, COL-017。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-025。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="82" hidden="0" customHeight="1">
+    <x:row r="49" ht="107" hidden="0" customHeight="1">
       <x:c r="A49" s="16" t="str">
         <x:v>COL-029</x:v>
       </x:c>
@@ -4097,13 +4129,13 @@
       <x:c r="P49" s="19" t="str"/>
       <x:c r="Q49" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-015, COL-019
-外部服务能力限制：G16
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-015, COL-019。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-029。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="69" hidden="0" customHeight="1">
+    <x:row r="50" ht="107" hidden="0" customHeight="1">
       <x:c r="A50" s="18" t="str">
         <x:v>COL-021</x:v>
       </x:c>
@@ -4150,12 +4182,13 @@
       <x:c r="P50" s="19" t="str"/>
       <x:c r="Q50" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-015, COL-016, COL-019, K-003, IF-010
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-015, COL-016, COL-019, K-003, IF-010。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-021。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="69" hidden="0" customHeight="1">
+    <x:row r="51" ht="107" hidden="0" customHeight="1">
       <x:c r="A51" s="16" t="str">
         <x:v>COL-022</x:v>
       </x:c>
@@ -4202,12 +4235,13 @@
       <x:c r="P51" s="19" t="str"/>
       <x:c r="Q51" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-012, COL-021, K-017
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-012, COL-021, K-017。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-022。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="69" hidden="0" customHeight="1">
+    <x:row r="52" ht="107" hidden="0" customHeight="1">
       <x:c r="A52" s="18" t="str">
         <x:v>COL-023</x:v>
       </x:c>
@@ -4254,12 +4288,13 @@
       <x:c r="P52" s="19" t="str"/>
       <x:c r="Q52" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-011, COL-022
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-011, COL-022。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-023。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="69" hidden="0" customHeight="1">
+    <x:row r="53" ht="107" hidden="0" customHeight="1">
       <x:c r="A53" s="16" t="str">
         <x:v>COL-024</x:v>
       </x:c>
@@ -4306,12 +4341,13 @@
       <x:c r="P53" s="19" t="str"/>
       <x:c r="Q53" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-012, COL-018, COL-019, COL-023
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-012, COL-018, COL-019, COL-023。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-024。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="69" hidden="0" customHeight="1">
+    <x:row r="54" ht="95" hidden="0" customHeight="1">
       <x:c r="A54" s="18" t="str">
         <x:v>K-004</x:v>
       </x:c>
@@ -4358,12 +4394,13 @@
       <x:c r="P54" s="19" t="str"/>
       <x:c r="Q54" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-001, K-003, COL-021
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-001, K-003, COL-021。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-004。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="82" hidden="0" customHeight="1">
+    <x:row r="55" ht="95" hidden="0" customHeight="1">
       <x:c r="A55" s="16" t="str">
         <x:v>K-005</x:v>
       </x:c>
@@ -4410,13 +4447,13 @@
       <x:c r="P55" s="19" t="str"/>
       <x:c r="Q55" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003, K-004, COL-021
-相关外部验收边界：X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003, K-004, COL-021。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-005。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="69" hidden="0" customHeight="1">
+    <x:row r="56" ht="95" hidden="0" customHeight="1">
       <x:c r="A56" s="18" t="str">
         <x:v>K-006</x:v>
       </x:c>
@@ -4463,12 +4500,13 @@
       <x:c r="P56" s="19" t="str"/>
       <x:c r="Q56" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003, K-005
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003, K-005。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-006。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="69" hidden="0" customHeight="1">
+    <x:row r="57" ht="95" hidden="0" customHeight="1">
       <x:c r="A57" s="16" t="str">
         <x:v>K-007</x:v>
       </x:c>
@@ -4515,12 +4553,13 @@
       <x:c r="P57" s="19" t="str"/>
       <x:c r="Q57" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003, K-006, COL-017, COL-019
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003, K-006, COL-017, COL-019。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-007。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="69" hidden="0" customHeight="1">
+    <x:row r="58" ht="95" hidden="0" customHeight="1">
       <x:c r="A58" s="18" t="str">
         <x:v>K-008</x:v>
       </x:c>
@@ -4567,12 +4606,13 @@
       <x:c r="P58" s="19" t="str"/>
       <x:c r="Q58" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-002, K-006
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-002, K-006。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-008。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="69" hidden="0" customHeight="1">
+    <x:row r="59" ht="95" hidden="0" customHeight="1">
       <x:c r="A59" s="16" t="str">
         <x:v>K-009</x:v>
       </x:c>
@@ -4619,12 +4659,13 @@
       <x:c r="P59" s="19" t="str"/>
       <x:c r="Q59" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-002, K-008
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-002, K-008。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-009。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="69" hidden="0" customHeight="1">
+    <x:row r="60" ht="95" hidden="0" customHeight="1">
       <x:c r="A60" s="18" t="str">
         <x:v>K-016</x:v>
       </x:c>
@@ -4671,12 +4712,13 @@
       <x:c r="P60" s="19" t="str"/>
       <x:c r="Q60" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-002, K-003, COL-002
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-002, K-003, COL-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-016。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="69" hidden="0" customHeight="1">
+    <x:row r="61" ht="95" hidden="0" customHeight="1">
       <x:c r="A61" s="16" t="str">
         <x:v>K-017</x:v>
       </x:c>
@@ -4723,12 +4765,13 @@
       <x:c r="P61" s="19" t="str"/>
       <x:c r="Q61" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003, K-008, K-016, IF-003, K-007, K-018
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003, K-008, K-016, IF-003, K-007, K-018。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-017。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="69" hidden="0" customHeight="1">
+    <x:row r="62" ht="95" hidden="0" customHeight="1">
       <x:c r="A62" s="18" t="str">
         <x:v>K-018</x:v>
       </x:c>
@@ -4775,12 +4818,13 @@
       <x:c r="P62" s="19" t="str"/>
       <x:c r="Q62" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-008, K-003, K-016
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-008, K-003, K-016。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-018。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="69" hidden="0" customHeight="1">
+    <x:row r="63" ht="95" hidden="0" customHeight="1">
       <x:c r="A63" s="16" t="str">
         <x:v>K-019</x:v>
       </x:c>
@@ -4827,12 +4871,13 @@
       <x:c r="P63" s="19" t="str"/>
       <x:c r="Q63" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-002, K-003, K-017, COL-013
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-002, K-003, K-017, COL-013。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-019。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="69" hidden="0" customHeight="1">
+    <x:row r="64" ht="95" hidden="0" customHeight="1">
       <x:c r="A64" s="18" t="str">
         <x:v>K-021</x:v>
       </x:c>
@@ -4879,12 +4924,13 @@
       <x:c r="P64" s="19" t="str"/>
       <x:c r="Q64" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-002, K-008
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-002, K-008。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-021。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="82" hidden="0" customHeight="1">
+    <x:row r="65" ht="95" hidden="0" customHeight="1">
       <x:c r="A65" s="16" t="str">
         <x:v>K-022</x:v>
       </x:c>
@@ -4931,13 +4977,13 @@
       <x:c r="P65" s="19" t="str"/>
       <x:c r="Q65" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-018, K-021, K-027, K-017
-相关外部验收边界：X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-018, K-021, K-027, K-017。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-022。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="69" hidden="0" customHeight="1">
+    <x:row r="66" ht="95" hidden="0" customHeight="1">
       <x:c r="A66" s="18" t="str">
         <x:v>K-023</x:v>
       </x:c>
@@ -4984,12 +5030,13 @@
       <x:c r="P66" s="19" t="str"/>
       <x:c r="Q66" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-021, K-022
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-021, K-022。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-023。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="69" hidden="0" customHeight="1">
+    <x:row r="67" ht="95" hidden="0" customHeight="1">
       <x:c r="A67" s="16" t="str">
         <x:v>K-024</x:v>
       </x:c>
@@ -5036,12 +5083,13 @@
       <x:c r="P67" s="19" t="str"/>
       <x:c r="Q67" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-018, K-023
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-018, K-023。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-024。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="82" hidden="0" customHeight="1">
+    <x:row r="68" ht="95" hidden="0" customHeight="1">
       <x:c r="A68" s="18" t="str">
         <x:v>K-025</x:v>
       </x:c>
@@ -5088,13 +5136,13 @@
       <x:c r="P68" s="19" t="str"/>
       <x:c r="Q68" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-002, K-019, K-024, COL-029
-外部服务能力限制：G16
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-002, K-019, K-024, COL-029。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-025。
 逐条验收：执行中 5。</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="69" hidden="0" customHeight="1">
+    <x:row r="69" ht="95" hidden="0" customHeight="1">
       <x:c r="A69" s="16" t="str">
         <x:v>IF-015</x:v>
       </x:c>
@@ -5141,12 +5189,13 @@
       <x:c r="P69" s="19" t="str"/>
       <x:c r="Q69" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-012, IF-014, K-026, K-027
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-012, IF-014, K-026, K-027。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-015。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="69" hidden="0" customHeight="1">
+    <x:row r="70" ht="95" hidden="0" customHeight="1">
       <x:c r="A70" s="18" t="str">
         <x:v>K-026</x:v>
       </x:c>
@@ -5193,12 +5242,13 @@
       <x:c r="P70" s="19" t="str"/>
       <x:c r="Q70" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-024, K-025
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-024, K-025。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-026。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="69" hidden="0" customHeight="1">
+    <x:row r="71" ht="95" hidden="0" customHeight="1">
       <x:c r="A71" s="16" t="str">
         <x:v>IF-011</x:v>
       </x:c>
@@ -5245,12 +5295,13 @@
       <x:c r="P71" s="19" t="str"/>
       <x:c r="Q71" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-010, K-017, COL-021, COL-022
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-010, K-017, COL-021, COL-022。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-011。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="69" hidden="0" customHeight="1">
+    <x:row r="72" ht="95" hidden="0" customHeight="1">
       <x:c r="A72" s="18" t="str">
         <x:v>IF-012</x:v>
       </x:c>
@@ -5297,12 +5348,13 @@
       <x:c r="P72" s="19" t="str"/>
       <x:c r="Q72" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-004, IF-006
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-004, IF-006。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-012。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="82" hidden="0" customHeight="1">
+    <x:row r="73" ht="95" hidden="0" customHeight="1">
       <x:c r="A73" s="16" t="str">
         <x:v>IF-013</x:v>
       </x:c>
@@ -5349,12 +5401,13 @@
       <x:c r="P73" s="19" t="str"/>
       <x:c r="Q73" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-007, IF-012, COL-008, COL-011, COL-012, COL-013, COL-023
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-007, IF-012, COL-008, COL-011, COL-012, COL-013, COL-023。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-013。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="69" hidden="0" customHeight="1">
+    <x:row r="74" ht="95" hidden="0" customHeight="1">
       <x:c r="A74" s="18" t="str">
         <x:v>IF-014</x:v>
       </x:c>
@@ -5401,8 +5454,9 @@
       <x:c r="P74" s="19" t="str"/>
       <x:c r="Q74" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-003, K-008, K-018, K-024
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-003, K-008, K-018, K-024。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-014。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
@@ -5453,13 +5507,13 @@
       <x:c r="P75" s="19" t="str"/>
       <x:c r="Q75" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-009, IF-011, COL-012, COL-018, COL-019, COL-024
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-009, IF-011, COL-012, COL-018, COL-019, COL-024。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-018。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="82" hidden="0" customHeight="1">
+    <x:row r="76" ht="95" hidden="0" customHeight="1">
       <x:c r="A76" s="18" t="str">
         <x:v>IF-019</x:v>
       </x:c>
@@ -5506,13 +5560,13 @@
       <x:c r="P76" s="19" t="str"/>
       <x:c r="Q76" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-008, IF-012, COL-005
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-008, IF-012, COL-005。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-019。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="82" hidden="0" customHeight="1">
+    <x:row r="77" ht="95" hidden="0" customHeight="1">
       <x:c r="A77" s="16" t="str">
         <x:v>IF-020</x:v>
       </x:c>
@@ -5559,13 +5613,13 @@
       <x:c r="P77" s="19" t="str"/>
       <x:c r="Q77" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-014, IF-018, K-021, K-022, K-023, K-024
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-014, IF-018, K-021, K-022, K-023, K-024。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-020。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="82" hidden="0" customHeight="1">
+    <x:row r="78" ht="95" hidden="0" customHeight="1">
       <x:c r="A78" s="18" t="str">
         <x:v>IF-021</x:v>
       </x:c>
@@ -5612,9 +5666,9 @@
       <x:c r="P78" s="19" t="str"/>
       <x:c r="Q78" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-014, IF-018, K-006, K-008, K-009, K-018
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-014, IF-018, K-006, K-008, K-009, K-018。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-021。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
@@ -5665,13 +5719,13 @@
       <x:c r="P79" s="19" t="str"/>
       <x:c r="Q79" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-017, IF-018, IF-020, IF-021, K-001, COL-018
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-017, IF-018, IF-020, IF-021, K-001, COL-018。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-022。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="82" hidden="0" customHeight="1">
+    <x:row r="80" ht="95" hidden="0" customHeight="1">
       <x:c r="A80" s="18" t="str">
         <x:v>IF-023</x:v>
       </x:c>
@@ -5718,13 +5772,13 @@
       <x:c r="P80" s="19" t="str"/>
       <x:c r="Q80" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-011, IF-018, IF-019, COL-019, COL-024
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-011, IF-018, IF-019, COL-019, COL-024。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-023。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="82" hidden="0" customHeight="1">
+    <x:row r="81" ht="95" hidden="0" customHeight="1">
       <x:c r="A81" s="16" t="str">
         <x:v>IF-027</x:v>
       </x:c>
@@ -5771,13 +5825,13 @@
       <x:c r="P81" s="19" t="str"/>
       <x:c r="Q81" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-020, K-025, COL-029
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-020, K-025, COL-029。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-027。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="82" hidden="0" customHeight="1">
+    <x:row r="82" ht="107" hidden="0" customHeight="1">
       <x:c r="A82" s="18" t="str">
         <x:v>COL-026</x:v>
       </x:c>
@@ -5824,12 +5878,13 @@
       <x:c r="P82" s="19" t="str"/>
       <x:c r="Q82" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-007, COL-010, COL-012, COL-018, COL-021, FND-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-007, COL-010, COL-012, COL-018, COL-021, FND-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-026。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="82" hidden="0" customHeight="1">
+    <x:row r="83" ht="120" hidden="0" customHeight="1">
       <x:c r="A83" s="16" t="str">
         <x:v>COL-027</x:v>
       </x:c>
@@ -5876,12 +5931,13 @@
       <x:c r="P83" s="19" t="str"/>
       <x:c r="Q83" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-010, COL-013, COL-017, COL-019, COL-022, COL-023, COL-025
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-010, COL-013, COL-017, COL-019, COL-022, COL-023, COL-025。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-027。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="107" hidden="0" customHeight="1">
+    <x:row r="84" ht="132" hidden="0" customHeight="1">
       <x:c r="A84" s="18" t="str">
         <x:v>COL-028</x:v>
       </x:c>
@@ -5928,13 +5984,14 @@
       <x:c r="P84" s="19" t="str"/>
       <x:c r="Q84" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：COL-024, COL-025, COL-026, COL-027, QA-001
-相关外部验收边界：X-SAMPLES, X-PLATFORM, X-DEPLOY, X-PILOT；逐条适用说明见独立矩阵。
-逐条验收：阻塞 3。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="82" hidden="0" customHeight="1">
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：原授权测试workspace双平台样本、实际调度周期和小范围灰度结果；关闭开关/恢复的工程子项单独已证。
+原直接依赖未签收：COL-024, COL-025, COL-026, COL-027, QA-001。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-028。
+逐条验收：阻塞 1，通过 1，执行中 1。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="95" hidden="0" customHeight="1">
       <x:c r="A85" s="16" t="str">
         <x:v>IF-029</x:v>
       </x:c>
@@ -5981,12 +6038,13 @@
       <x:c r="P85" s="19" t="str"/>
       <x:c r="Q85" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-004, IF-008, IF-010, IF-014, COL-026, K-030
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-004, IF-008, IF-010, IF-014, COL-026, K-030。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-029。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="82" hidden="0" customHeight="1">
+    <x:row r="86" ht="95" hidden="0" customHeight="1">
       <x:c r="A86" s="18" t="str">
         <x:v>K-030</x:v>
       </x:c>
@@ -6033,12 +6091,13 @@
       <x:c r="P86" s="19" t="str"/>
       <x:c r="Q86" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-004, K-007, K-008, K-016, K-017, K-023, K-024, K-025, FND-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-004, K-007, K-008, K-016, K-017, K-023, K-024, K-025, FND-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-030。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="107" hidden="0" customHeight="1">
+    <x:row r="87" ht="132" hidden="0" customHeight="1">
       <x:c r="A87" s="16" t="str">
         <x:v>QA-001</x:v>
       </x:c>
@@ -6085,13 +6144,14 @@
       <x:c r="P87" s="19" t="str"/>
       <x:c r="Q87" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：IF-013, IF-015, IF-022, IF-023, IF-027, IF-029, COL-027, K-030, FND-003
-相关外部验收边界：X-DOMAIN, X-SAMPLES, X-PLATFORM, X-MODELS, X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：原真实双平台手工/MCP/账号定时完整样本验收；原生宿主Agent/Canvas不能再列未实现。
+原直接依赖未签收：IF-013, IF-015, IF-022, IF-023, IF-027, IF-029, COL-027, K-030, FND-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 QA-001。
 逐条验收：阻塞 1。</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="69" hidden="0" customHeight="1">
+    <x:row r="88" ht="82" hidden="0" customHeight="1">
       <x:c r="A88" s="18" t="str">
         <x:v>K-010</x:v>
       </x:c>
@@ -6138,12 +6198,13 @@
       <x:c r="P88" s="19" t="str"/>
       <x:c r="Q88" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-010。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="69" hidden="0" customHeight="1">
+    <x:row r="89" ht="95" hidden="0" customHeight="1">
       <x:c r="A89" s="16" t="str">
         <x:v>K-011</x:v>
       </x:c>
@@ -6190,12 +6251,13 @@
       <x:c r="P89" s="19" t="str"/>
       <x:c r="Q89" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-001, K-010
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-001, K-010。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-011。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="82" hidden="0" customHeight="1">
+    <x:row r="90" ht="95" hidden="0" customHeight="1">
       <x:c r="A90" s="18" t="str">
         <x:v>K-012</x:v>
       </x:c>
@@ -6242,13 +6304,13 @@
       <x:c r="P90" s="19" t="str"/>
       <x:c r="Q90" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003, K-011
-相关外部验收边界：X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003, K-011。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-012。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="82" hidden="0" customHeight="1">
+    <x:row r="91" ht="95" hidden="0" customHeight="1">
       <x:c r="A91" s="16" t="str">
         <x:v>K-013</x:v>
       </x:c>
@@ -6295,13 +6357,13 @@
       <x:c r="P91" s="19" t="str"/>
       <x:c r="Q91" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-011, K-012
-相关外部验收边界：X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-011, K-012。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-013。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="82" hidden="0" customHeight="1">
+    <x:row r="92" ht="95" hidden="0" customHeight="1">
       <x:c r="A92" s="18" t="str">
         <x:v>K-014</x:v>
       </x:c>
@@ -6348,13 +6410,13 @@
       <x:c r="P92" s="19" t="str"/>
       <x:c r="Q92" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-003, K-007, K-013
-相关外部验收边界：X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-003, K-007, K-013。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-014。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="69" hidden="0" customHeight="1">
+    <x:row r="93" ht="95" hidden="0" customHeight="1">
       <x:c r="A93" s="16" t="str">
         <x:v>K-015</x:v>
       </x:c>
@@ -6401,12 +6463,13 @@
       <x:c r="P93" s="19" t="str"/>
       <x:c r="Q93" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-008, K-012, K-013
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-008, K-012, K-013。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-015。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="82" hidden="0" customHeight="1">
+    <x:row r="94" ht="120" hidden="0" customHeight="1">
       <x:c r="A94" s="18" t="str">
         <x:v>K-020</x:v>
       </x:c>
@@ -6429,7 +6492,7 @@
         <x:v>knowledge</x:v>
       </x:c>
       <x:c r="H94" s="19" t="str">
-        <x:v>待验收</x:v>
+        <x:v>阻塞</x:v>
       </x:c>
       <x:c r="I94" s="24" t="n">
         <x:v>2.5</x:v>
@@ -6443,7 +6506,7 @@
       </x:c>
       <x:c r="L94" s="18" t="str">
         <x:f>IF(H94="已完成","已完成",IF(D94="P2","后续规划",IF(H94="阻塞","处理阻塞",IF(H94="暂停","已暂停",IF(K94&gt;0,"等待依赖",IF(G94="","待指派",IF(H94="待验收","待验收","可推进")))))))</x:f>
-        <x:v>等待依赖</x:v>
+        <x:v>处理阻塞</x:v>
       </x:c>
       <x:c r="M94" s="18" t="str">
         <x:v>R14</x:v>
@@ -6453,13 +6516,14 @@
       <x:c r="P94" s="19" t="str"/>
       <x:c r="Q94" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-019, K-021
-相关外部验收边界：X-SAMPLES；逐条适用说明见独立矩阵。
-逐条验收：执行中 3。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="69" hidden="0" customHeight="1">
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：原验收中的授权正负样本匹配阈值校准；转载不计独立佐证、人工拆分和审计的工程门禁单独已证。
+原直接依赖未签收：K-019, K-021。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-020。
+逐条验收：通过 2，阻塞 1。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="95" hidden="0" customHeight="1">
       <x:c r="A95" s="16" t="str">
         <x:v>K-029</x:v>
       </x:c>
@@ -6506,12 +6570,13 @@
       <x:c r="P95" s="19" t="str"/>
       <x:c r="Q95" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-020, K-023, K-024
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-020, K-023, K-024。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-029。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="82" hidden="0" customHeight="1">
+    <x:row r="96" ht="95" hidden="0" customHeight="1">
       <x:c r="A96" s="18" t="str">
         <x:v>IF-025</x:v>
       </x:c>
@@ -6558,9 +6623,9 @@
       <x:c r="P96" s="19" t="str"/>
       <x:c r="Q96" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-020, IF-015, K-028, K-029
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-020, IF-015, K-028, K-029。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-025。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
@@ -6611,13 +6676,13 @@
       <x:c r="P97" s="19" t="str"/>
       <x:c r="Q97" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-025, K-028, K-026, QA-002
-相关外部验收边界：X-BROWSER, X-DEPLOY；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-025, K-028, K-026, QA-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-026。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="82" hidden="0" customHeight="1">
+    <x:row r="98" ht="95" hidden="0" customHeight="1">
       <x:c r="A98" s="18" t="str">
         <x:v>K-028</x:v>
       </x:c>
@@ -6664,13 +6729,13 @@
       <x:c r="P98" s="19" t="str"/>
       <x:c r="Q98" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-024, K-026, K-027, K-029
-相关外部验收边界：X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-024, K-026, K-027, K-029。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-028。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="82" hidden="0" customHeight="1">
+    <x:row r="99" ht="95" hidden="0" customHeight="1">
       <x:c r="A99" s="16" t="str">
         <x:v>IF-024</x:v>
       </x:c>
@@ -6717,13 +6782,13 @@
       <x:c r="P99" s="19" t="str"/>
       <x:c r="Q99" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-021, IF-022, K-011, K-012, K-013, K-015
-相关外部验收边界：X-BROWSER；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-021, IF-022, K-011, K-012, K-013, K-015。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-024。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="95" hidden="0" customHeight="1">
+    <x:row r="100" ht="107" hidden="0" customHeight="1">
       <x:c r="A100" s="18" t="str">
         <x:v>COL-030</x:v>
       </x:c>
@@ -6770,13 +6835,13 @@
       <x:c r="P100" s="19" t="str"/>
       <x:c r="Q100" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：COL-009, COL-010, COL-022, COL-028, K-016, K-025
-相关外部验收边界：X-PLATFORM；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：COL-009, COL-010, COL-022, COL-028, K-016, K-025。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-030。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="82" hidden="0" customHeight="1">
+    <x:row r="101" ht="95" hidden="0" customHeight="1">
       <x:c r="A101" s="16" t="str">
         <x:v>QA-002</x:v>
       </x:c>
@@ -6823,13 +6888,13 @@
       <x:c r="P101" s="19" t="str"/>
       <x:c r="Q101" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-028, IF-015, FND-004
-相关外部验收边界：X-DEPLOY；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-028, IF-015, FND-004。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 QA-002。
 逐条验收：执行中 1。</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="107" hidden="0" customHeight="1">
+    <x:row r="102" ht="145" hidden="0" customHeight="1">
       <x:c r="A102" s="18" t="str">
         <x:v>COL-031</x:v>
       </x:c>
@@ -6876,10 +6941,11 @@
       <x:c r="P102" s="19" t="str"/>
       <x:c r="Q102" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：COL-028, COL-029, COL-030, IF-028, K-031, QA-002
-相关外部验收边界：X-SAMPLES, X-MODELS, X-PILOT；逐条适用说明见独立矩阵。
-逐条验收：阻塞 3。</x:v>
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：目标CPU/RAM/磁盘/模型和真实视频分布容量、授权上游测试实例/小范围样本灰度；不得把本地worker基线泛化SLO，完整V1仍取决于原全部验收。
+原直接依赖未签收：COL-028, COL-029, COL-030, IF-028, K-031, QA-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 COL-031。
+逐条验收：执行中 2，阻塞 1。</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="95" hidden="0" customHeight="1">
@@ -6929,9 +6995,9 @@
       <x:c r="P103" s="19" t="str"/>
       <x:c r="Q103" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：IF-028, IF-029, COL-025, COL-028, COL-031, K-031
-相关外部验收边界：X-DEPLOY；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：IF-028, IF-029, COL-025, COL-028, COL-031, K-031。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-030。
 逐条验收：执行中 4。</x:v>
       </x:c>
     </x:row>
@@ -6982,13 +7048,13 @@
       <x:c r="P104" s="19" t="str"/>
       <x:c r="Q104" s="19" t="str">
         <x:v>【执行记录】
-当前实现与针对性证据可供验收；最终同一源码快照、真实宿主/平台或任务专项条款尚未由本审计全部正式认证。
-前置任务未正式闭合：K-007, K-017, K-022, K-028
-相关外部验收边界：X-SAMPLES, X-MODELS；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原直接依赖未签收：K-007, K-017, K-022, K-028。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 K-031。
 逐条验收：执行中 3。</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="107" hidden="0" customHeight="1">
+    <x:row r="105" ht="132" hidden="0" customHeight="1">
       <x:c r="A105" s="16" t="str">
         <x:v>IF-028</x:v>
       </x:c>
@@ -7035,13 +7101,14 @@
       <x:c r="P105" s="19" t="str"/>
       <x:c r="Q105" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：IF-013, IF-020, IF-024, IF-026, COL-023, COL-027, K-030
-相关外部验收边界：X-SAMPLES, X-PLATFORM, X-BROWSER；逐条适用说明见独立矩阵。
-逐条验收：阻塞 4。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="107" hidden="0" customHeight="1">
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：B站/抖音各字幕、无字幕、长视频及视觉必需授权样本的原覆盖；内部跨入口/真实Canvas/hash/replay工程证据独立保留。
+原直接依赖未签收：IF-013, IF-020, IF-024, IF-026, COL-023, COL-027, K-030。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 IF-028。
+逐条验收：阻塞 1，通过 3。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="132" hidden="0" customHeight="1">
       <x:c r="A106" s="18" t="str">
         <x:v>QA-003</x:v>
       </x:c>
@@ -7088,9 +7155,10 @@
       <x:c r="P106" s="19" t="str"/>
       <x:c r="Q106" s="19" t="str">
         <x:v>【执行记录】
-缺少原条款要求的真实业务/样本/持续运行或最终打包证据；实现与此门禁分开。
-前置任务未正式闭合：IF-028, IF-029, IF-030, COL-031, K-031, QA-001, QA-002
-相关外部验收边界：X-DOMAIN, X-SAMPLES, X-PLATFORM, X-MODELS, X-DEPLOY, X-PILOT；逐条适用说明见独立矩阵。
+自身工程实现及范围化执行证据已核验（应用源码 ff03a18）；不等于原整项验收及依赖已签收。
+原条款待输入：按M0冻结实际时长持续试点、三基线质量比较、偏差与项目方签收；默认建议7天，不能压缩/虚构，TEST不默认需要生产授权。
+原直接依赖未签收：IF-028, IF-029, IF-030, COL-031, K-031, QA-001, QA-002。这是验收依赖，不是未实现代码清单。
+本任务证据、执行范围与边界见 V1-CLOSURE.md 和矩阵 QA-003。
 逐条验收：阻塞 1。</x:v>
       </x:c>
     </x:row>
@@ -7462,7 +7530,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R271611134c2f4bc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b26285d89c54d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11682,7 +11750,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa048be624e4d5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8c2310abae646ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12602,7 +12670,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72105ce66b4d4df6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28e5e97610fa44d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12751,11 +12819,17 @@
         <x:v>R02 R06 R07 R11 R15 R16</x:v>
       </x:c>
       <x:c r="H7" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I7" s="19" t="str"/>
-      <x:c r="J7" s="19" t="str"/>
-      <x:c r="K7" s="19" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="I7" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J7" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/0</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="str">
+        <x:v>原验收前置待补（非未关闭工程缺陷）：待合法B站实际获取与已冻结领域配置的原业务验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="64" hidden="0" customHeight="1">
       <x:c r="A8" s="18" t="str">
@@ -12780,11 +12854,17 @@
         <x:v>R02 R06 R11</x:v>
       </x:c>
       <x:c r="H8" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I8" s="19" t="str"/>
-      <x:c r="J8" s="19" t="str"/>
-      <x:c r="K8" s="19" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="I8" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/1</x:v>
+      </x:c>
+      <x:c r="K8" s="19" t="str">
+        <x:v>原验收前置待补（非未关闭工程缺陷）：待可用抖音分享短链/授权连接的真实获取；不把fixture当平台成功。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="64" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -12809,11 +12889,17 @@
         <x:v>R03 R20</x:v>
       </x:c>
       <x:c r="H9" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I9" s="19" t="str"/>
-      <x:c r="J9" s="19" t="str"/>
-      <x:c r="K9" s="19" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="I9" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/2</x:v>
+      </x:c>
+      <x:c r="K9" s="19" t="str">
+        <x:v>原验收前置待补（非未关闭工程缺陷）：原两个平台真实账号与实际窗口/重新登录验收仍需对应来源；不以加速时钟替代。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="64" hidden="0" customHeight="1">
       <x:c r="A10" s="18" t="str">
@@ -12838,10 +12924,14 @@
         <x:v>R04 R23</x:v>
       </x:c>
       <x:c r="H10" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I10" s="19" t="str"/>
-      <x:c r="J10" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I10" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/3</x:v>
+      </x:c>
       <x:c r="K10" s="19" t="str"/>
     </x:row>
     <x:row r="11" ht="64" hidden="0" customHeight="1">
@@ -12867,10 +12957,14 @@
         <x:v>R05 R17</x:v>
       </x:c>
       <x:c r="H11" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I11" s="19" t="str"/>
-      <x:c r="J11" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I11" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J11" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/4</x:v>
+      </x:c>
       <x:c r="K11" s="19" t="str"/>
     </x:row>
     <x:row r="12" ht="64" hidden="0" customHeight="1">
@@ -12896,10 +12990,14 @@
         <x:v>R05 R23</x:v>
       </x:c>
       <x:c r="H12" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I12" s="19" t="str"/>
-      <x:c r="J12" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I12" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J12" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/5</x:v>
+      </x:c>
       <x:c r="K12" s="19" t="str"/>
     </x:row>
     <x:row r="13" ht="64" hidden="0" customHeight="1">
@@ -12925,10 +13023,14 @@
         <x:v>R23 R25</x:v>
       </x:c>
       <x:c r="H13" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I13" s="19" t="str"/>
-      <x:c r="J13" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I13" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J13" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/6</x:v>
+      </x:c>
       <x:c r="K13" s="19" t="str"/>
     </x:row>
     <x:row r="14" ht="64" hidden="0" customHeight="1">
@@ -12954,10 +13056,14 @@
         <x:v>R07 R11</x:v>
       </x:c>
       <x:c r="H14" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I14" s="19" t="str"/>
-      <x:c r="J14" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I14" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J14" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/7</x:v>
+      </x:c>
       <x:c r="K14" s="19" t="str"/>
     </x:row>
     <x:row r="15" ht="64" hidden="0" customHeight="1">
@@ -12983,10 +13089,14 @@
         <x:v>R08 R12</x:v>
       </x:c>
       <x:c r="H15" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I15" s="19" t="str"/>
-      <x:c r="J15" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I15" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J15" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/8</x:v>
+      </x:c>
       <x:c r="K15" s="19" t="str"/>
     </x:row>
     <x:row r="16" ht="64" hidden="0" customHeight="1">
@@ -13012,10 +13122,14 @@
         <x:v>R09 R11 R12</x:v>
       </x:c>
       <x:c r="H16" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I16" s="19" t="str"/>
-      <x:c r="J16" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I16" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J16" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/9</x:v>
+      </x:c>
       <x:c r="K16" s="19" t="str"/>
     </x:row>
     <x:row r="17" ht="64" hidden="0" customHeight="1">
@@ -13041,10 +13155,14 @@
         <x:v>R10</x:v>
       </x:c>
       <x:c r="H17" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I17" s="19" t="str"/>
-      <x:c r="J17" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I17" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J17" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/10</x:v>
+      </x:c>
       <x:c r="K17" s="19" t="str"/>
     </x:row>
     <x:row r="18" ht="64" hidden="0" customHeight="1">
@@ -13070,10 +13188,14 @@
         <x:v>R11</x:v>
       </x:c>
       <x:c r="H18" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I18" s="19" t="str"/>
-      <x:c r="J18" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I18" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J18" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/11</x:v>
+      </x:c>
       <x:c r="K18" s="19" t="str"/>
     </x:row>
     <x:row r="19" ht="64" hidden="0" customHeight="1">
@@ -13099,10 +13221,14 @@
         <x:v>R12</x:v>
       </x:c>
       <x:c r="H19" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I19" s="19" t="str"/>
-      <x:c r="J19" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I19" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J19" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/12</x:v>
+      </x:c>
       <x:c r="K19" s="19" t="str"/>
     </x:row>
     <x:row r="20" ht="64" hidden="0" customHeight="1">
@@ -13128,11 +13254,17 @@
         <x:v>R13 R15</x:v>
       </x:c>
       <x:c r="H20" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I20" s="19" t="str"/>
-      <x:c r="J20" s="19" t="str"/>
-      <x:c r="K20" s="19" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="I20" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J20" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/13</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="str">
+        <x:v>原验收前置待补（非未关闭工程缺陷）：真实所选模型对缺参材料的语义拒答/推断标记及人工判定仍未由确定性fixture证明；与AC27质量输入合并，不说缺实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="64" hidden="0" customHeight="1">
       <x:c r="A21" s="16" t="str">
@@ -13157,10 +13289,14 @@
         <x:v>R14</x:v>
       </x:c>
       <x:c r="H21" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I21" s="19" t="str"/>
-      <x:c r="J21" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I21" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J21" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/14</x:v>
+      </x:c>
       <x:c r="K21" s="19" t="str"/>
     </x:row>
     <x:row r="22" ht="64" hidden="0" customHeight="1">
@@ -13186,10 +13322,14 @@
         <x:v>R15 R16 R25</x:v>
       </x:c>
       <x:c r="H22" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I22" s="19" t="str"/>
-      <x:c r="J22" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I22" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J22" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/15</x:v>
+      </x:c>
       <x:c r="K22" s="19" t="str"/>
     </x:row>
     <x:row r="23" ht="64" hidden="0" customHeight="1">
@@ -13215,10 +13355,14 @@
         <x:v>R21</x:v>
       </x:c>
       <x:c r="H23" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I23" s="19" t="str"/>
-      <x:c r="J23" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I23" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J23" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/16</x:v>
+      </x:c>
       <x:c r="K23" s="19" t="str"/>
     </x:row>
     <x:row r="24" ht="64" hidden="0" customHeight="1">
@@ -13244,10 +13388,14 @@
         <x:v>R17</x:v>
       </x:c>
       <x:c r="H24" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I24" s="19" t="str"/>
-      <x:c r="J24" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I24" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J24" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/17</x:v>
+      </x:c>
       <x:c r="K24" s="19" t="str"/>
     </x:row>
     <x:row r="25" ht="64" hidden="0" customHeight="1">
@@ -13273,10 +13421,14 @@
         <x:v>R22</x:v>
       </x:c>
       <x:c r="H25" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I25" s="19" t="str"/>
-      <x:c r="J25" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I25" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J25" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/18</x:v>
+      </x:c>
       <x:c r="K25" s="19" t="str"/>
     </x:row>
     <x:row r="26" ht="64" hidden="0" customHeight="1">
@@ -13302,10 +13454,14 @@
         <x:v>R18 R22</x:v>
       </x:c>
       <x:c r="H26" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I26" s="19" t="str"/>
-      <x:c r="J26" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I26" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J26" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/19</x:v>
+      </x:c>
       <x:c r="K26" s="19" t="str"/>
     </x:row>
     <x:row r="27" ht="64" hidden="0" customHeight="1">
@@ -13331,10 +13487,14 @@
         <x:v>R02 R23</x:v>
       </x:c>
       <x:c r="H27" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I27" s="19" t="str"/>
-      <x:c r="J27" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I27" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J27" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/20</x:v>
+      </x:c>
       <x:c r="K27" s="19" t="str"/>
     </x:row>
     <x:row r="28" ht="64" hidden="0" customHeight="1">
@@ -13360,10 +13520,14 @@
         <x:v>R24</x:v>
       </x:c>
       <x:c r="H28" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I28" s="19" t="str"/>
-      <x:c r="J28" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I28" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J28" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/21</x:v>
+      </x:c>
       <x:c r="K28" s="19" t="str"/>
     </x:row>
     <x:row r="29" ht="64" hidden="0" customHeight="1">
@@ -13389,10 +13553,14 @@
         <x:v>R25</x:v>
       </x:c>
       <x:c r="H29" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I29" s="19" t="str"/>
-      <x:c r="J29" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I29" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J29" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/22</x:v>
+      </x:c>
       <x:c r="K29" s="19" t="str"/>
     </x:row>
     <x:row r="30" ht="64" hidden="0" customHeight="1">
@@ -13418,10 +13586,14 @@
         <x:v>R26 R28</x:v>
       </x:c>
       <x:c r="H30" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I30" s="19" t="str"/>
-      <x:c r="J30" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I30" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J30" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/23</x:v>
+      </x:c>
       <x:c r="K30" s="19" t="str"/>
     </x:row>
     <x:row r="31" ht="64" hidden="0" customHeight="1">
@@ -13447,10 +13619,14 @@
         <x:v>R16 R18</x:v>
       </x:c>
       <x:c r="H31" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I31" s="19" t="str"/>
-      <x:c r="J31" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I31" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J31" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/24</x:v>
+      </x:c>
       <x:c r="K31" s="19" t="str"/>
     </x:row>
     <x:row r="32" ht="64" hidden="0" customHeight="1">
@@ -13476,10 +13652,14 @@
         <x:v>R19</x:v>
       </x:c>
       <x:c r="H32" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I32" s="19" t="str"/>
-      <x:c r="J32" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I32" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J32" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/25</x:v>
+      </x:c>
       <x:c r="K32" s="19" t="str"/>
     </x:row>
     <x:row r="33" ht="64" hidden="0" customHeight="1">
@@ -13505,11 +13685,17 @@
         <x:v>R19 R27</x:v>
       </x:c>
       <x:c r="H33" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I33" s="19" t="str"/>
-      <x:c r="J33" s="19" t="str"/>
-      <x:c r="K33" s="19" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="I33" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J33" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/26</x:v>
+      </x:c>
+      <x:c r="K33" s="19" t="str">
+        <x:v>原验收前置待补（非未关闭工程缺陷）：真实行业固定集/独立人工金标与所选模型结果比较未验收；exact_expected_output_v1不是模型质量结论。</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="64" hidden="0" customHeight="1">
       <x:c r="A34" s="18" t="str">
@@ -13534,10 +13720,14 @@
         <x:v>R28</x:v>
       </x:c>
       <x:c r="H34" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I34" s="19" t="str"/>
-      <x:c r="J34" s="19" t="str"/>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I34" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J34" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/27</x:v>
+      </x:c>
       <x:c r="K34" s="19" t="str"/>
     </x:row>
     <x:row r="35" ht="64" hidden="0" customHeight="1">
@@ -13563,11 +13753,17 @@
         <x:v>R03 R24 R27</x:v>
       </x:c>
       <x:c r="H35" s="19" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="I35" s="19" t="str"/>
-      <x:c r="J35" s="19" t="str"/>
-      <x:c r="K35" s="19" t="str"/>
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="I35" s="19" t="str">
+        <x:v>dot 工程审核与独立复核（受控 TEST；非行业业务签收）</x:v>
+      </x:c>
+      <x:c r="J35" s="19" t="str">
+        <x:v>docs/video-ingestion/evidence/v1-closure-matrix.json#/acceptance_cases/28</x:v>
+      </x:c>
+      <x:c r="K35" s="19" t="str">
+        <x:v>原验收前置待补（非未关闭工程缺陷）：待M0真实来源/样本/配置/预算及冻结时长连续运行和结果核对；默认建议7天，不压缩/虚构，TEST不默认要求生产授权。</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="64" hidden="0" customHeight="1">
       <x:c r="A36" s="18" t="str">
@@ -13661,7 +13857,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd14615b451749ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac813e43a9974e86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14803,9 +14999,9 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="3">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54d021567e04e8b"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de96c6a0b504fec"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3cb288d29d047b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0eebae1861d4896"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re56d222a3dd442a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R138648daa2574662"/>
   </x:tableParts>
 </x:worksheet>
 </file>